--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 02/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Back_Summary.xlsx
@@ -437,6 +437,16 @@
           <t>Radius</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -450,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.10349</v>
+        <v>17.4249</v>
       </c>
       <c r="D2" t="n">
-        <v>17.21296</v>
+        <v>17.18551</v>
       </c>
       <c r="E2" t="n">
-        <v>17.22431</v>
+        <v>17.34876</v>
       </c>
       <c r="F2" t="n">
-        <v>43.28958</v>
+        <v>43.99665</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05274</v>
+        <v>0.05122</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86953</v>
+        <v>1.86476</v>
       </c>
     </row>
     <row r="3">
@@ -475,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.3632</v>
+        <v>17.36394</v>
       </c>
       <c r="D3" t="n">
-        <v>16.68953</v>
+        <v>16.80888</v>
       </c>
       <c r="E3" t="n">
-        <v>17.3898</v>
+        <v>17.17867</v>
       </c>
       <c r="F3" t="n">
-        <v>43.49668</v>
+        <v>43.2507</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05243</v>
+        <v>0.05258</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8754</v>
+        <v>1.84041</v>
       </c>
     </row>
     <row r="4">
@@ -500,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.48458</v>
+        <v>17.31513</v>
       </c>
       <c r="D4" t="n">
-        <v>17.06756</v>
+        <v>17.08031</v>
       </c>
       <c r="E4" t="n">
-        <v>17.49662</v>
+        <v>17.27357</v>
       </c>
       <c r="F4" t="n">
-        <v>43.30861</v>
+        <v>43.95618</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05192</v>
+        <v>0.05171</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93031</v>
+        <v>1.93436</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.4976</v>
+        <v>17.36323</v>
       </c>
       <c r="D5" t="n">
-        <v>17.27795</v>
+        <v>17.10609</v>
       </c>
       <c r="E5" t="n">
-        <v>17.16474</v>
+        <v>17.32546</v>
       </c>
       <c r="F5" t="n">
-        <v>43.3091</v>
+        <v>43.3937</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05226</v>
+        <v>0.05193</v>
       </c>
       <c r="H5" t="n">
-        <v>1.87487</v>
+        <v>1.85199</v>
       </c>
     </row>
     <row r="6">
@@ -549,23 +559,10 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>17.54233</v>
-      </c>
-      <c r="D6" t="n">
-        <v>17.25065</v>
-      </c>
-      <c r="E6" t="n">
-        <v>17.52699</v>
-      </c>
-      <c r="F6" t="n">
-        <v>43.78269</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.05266</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.86564</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>scratched - not measurable</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -575,22 +572,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.13762</v>
+        <v>17.15124</v>
       </c>
       <c r="D7" t="n">
-        <v>17.05515</v>
+        <v>17.07861</v>
       </c>
       <c r="E7" t="n">
-        <v>17.02592</v>
+        <v>17.14442</v>
       </c>
       <c r="F7" t="n">
-        <v>44.13491</v>
+        <v>42.66598</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05156</v>
+        <v>0.05204</v>
       </c>
       <c r="H7" t="n">
-        <v>1.86984</v>
+        <v>1.88068</v>
       </c>
     </row>
     <row r="8">
@@ -600,22 +597,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.89677</v>
+        <v>17.4155</v>
       </c>
       <c r="D8" t="n">
-        <v>17.0948</v>
+        <v>16.91035</v>
       </c>
       <c r="E8" t="n">
-        <v>16.86949</v>
+        <v>16.91191</v>
       </c>
       <c r="F8" t="n">
-        <v>43.2333</v>
+        <v>44.91422</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05251</v>
+        <v>0.05082</v>
       </c>
       <c r="H8" t="n">
-        <v>1.88952</v>
+        <v>1.88614</v>
       </c>
     </row>
     <row r="9">
@@ -625,22 +622,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.42841</v>
+        <v>17.47165</v>
       </c>
       <c r="D9" t="n">
-        <v>16.82148</v>
+        <v>16.80985</v>
       </c>
       <c r="E9" t="n">
-        <v>17.18531</v>
+        <v>16.908</v>
       </c>
       <c r="F9" t="n">
-        <v>44.55671</v>
+        <v>43.02689</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05223</v>
+        <v>0.0513</v>
       </c>
       <c r="H9" t="n">
-        <v>1.84262</v>
+        <v>1.88829</v>
       </c>
     </row>
     <row r="10">
@@ -650,33 +647,48 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.54963</v>
+        <v>17.31902</v>
       </c>
       <c r="D10" t="n">
-        <v>17.13371</v>
+        <v>16.76931</v>
       </c>
       <c r="E10" t="n">
-        <v>17.24392</v>
+        <v>17.1628</v>
       </c>
       <c r="F10" t="n">
-        <v>44.61849</v>
+        <v>44.01043</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05219</v>
+        <v>0.05083</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85255</v>
+        <v>1.84943</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -688,14 +700,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6400400000000001</v>
+        <v>17.34878</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13611</v>
+        <v>16.5561</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.80816</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22.37433</v>
+      </c>
+      <c r="G12" t="n">
+        <v>35.71402</v>
       </c>
     </row>
     <row r="13">
@@ -705,10 +726,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.61336</v>
+        <v>17.29186</v>
       </c>
       <c r="D13" t="n">
-        <v>1.14722</v>
+        <v>16.9136</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.92129</v>
+      </c>
+      <c r="F13" t="n">
+        <v>21.91798</v>
+      </c>
+      <c r="G13" t="n">
+        <v>34.72045</v>
       </c>
     </row>
     <row r="14">
@@ -717,11 +747,25 @@
           <t>Unit 9</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>re-measured</t>
+        </is>
+      </c>
       <c r="C14" t="n">
-        <v>0.61568</v>
+        <v>17.4715</v>
       </c>
       <c r="D14" t="n">
-        <v>1.14073</v>
+        <v>16.40146</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.58772</v>
+      </c>
+      <c r="F14" t="n">
+        <v>22.10764</v>
+      </c>
+      <c r="G14" t="n">
+        <v>35.53725</v>
       </c>
     </row>
     <row r="15">
@@ -731,10 +775,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.62194</v>
+        <v>17.3535</v>
       </c>
       <c r="D15" t="n">
-        <v>1.14727</v>
+        <v>16.39921</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.05907</v>
+      </c>
+      <c r="F15" t="n">
+        <v>21.90129</v>
+      </c>
+      <c r="G15" t="n">
+        <v>34.62178</v>
       </c>
     </row>
     <row r="16">
@@ -744,10 +797,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.62061</v>
+        <v>17.20892</v>
       </c>
       <c r="D16" t="n">
-        <v>1.13591</v>
+        <v>16.48226</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.97288</v>
+      </c>
+      <c r="F16" t="n">
+        <v>22.15179</v>
+      </c>
+      <c r="G16" t="n">
+        <v>35.0218</v>
       </c>
     </row>
     <row r="17">
@@ -757,10 +819,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.6261</v>
+        <v>17.59049</v>
       </c>
       <c r="D17" t="n">
-        <v>1.16364</v>
+        <v>16.38357</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.11733</v>
+      </c>
+      <c r="F17" t="n">
+        <v>22.50274</v>
+      </c>
+      <c r="G17" t="n">
+        <v>35.36215</v>
       </c>
     </row>
     <row r="18">
@@ -770,10 +841,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.62512</v>
+        <v>17.20411</v>
       </c>
       <c r="D18" t="n">
-        <v>1.13234</v>
+        <v>16.04474</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.88636</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22.21513</v>
+      </c>
+      <c r="G18" t="n">
+        <v>35.57969</v>
       </c>
     </row>
     <row r="19">
@@ -783,10 +863,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60931</v>
+        <v>16.99691</v>
       </c>
       <c r="D19" t="n">
-        <v>1.12686</v>
+        <v>16.75744</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.79868</v>
+      </c>
+      <c r="F19" t="n">
+        <v>22.53547</v>
+      </c>
+      <c r="G19" t="n">
+        <v>36.19087</v>
       </c>
     </row>
     <row r="20">
@@ -796,10 +885,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.60511</v>
+        <v>17.30096</v>
       </c>
       <c r="D20" t="n">
-        <v>1.14968</v>
+        <v>16.39599</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.73458</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22.41311</v>
+      </c>
+      <c r="G20" t="n">
+        <v>34.49487</v>
       </c>
     </row>
   </sheetData>
